--- a/data/trans_orig/P37A$otros-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P37A$otros-Edad-trans_orig.xlsx
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4217</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4400</t>
+          <t>4235</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>463272</t>
+          <t>463080</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>957153</t>
+          <t>957318</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7719</t>
+          <t>5219</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5790</t>
+          <t>6459</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>727770</t>
+          <t>730270</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1355192</t>
+          <t>1354523</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6184</t>
+          <t>5919</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4891</t>
+          <t>4589</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7583</t>
+          <t>8176</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>632484</t>
+          <t>632749</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>684853</t>
+          <t>685155</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1320829</t>
+          <t>1320236</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4971</t>
+          <t>5565</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4968</t>
+          <t>4980</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>510671</t>
+          <t>510077</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1029821</t>
+          <t>1029809</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4250</t>
+          <t>3900</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>4611</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>288333</t>
+          <t>288683</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>631429</t>
+          <t>630906</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7909</t>
+          <t>7284</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6621</t>
+          <t>7488</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>325999</t>
+          <t>326624</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>537170</t>
+          <t>536303</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>876</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8415</t>
+          <t>8839</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>984</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10156</t>
+          <t>10786</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3806</t>
+          <t>3725</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15158</t>
+          <t>15682</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3268128</t>
+          <t>3267704</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3275663</t>
+          <t>3275667</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3369041</t>
+          <t>3368411</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3378211</t>
+          <t>3378213</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6640583</t>
+          <t>6640059</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6651935</t>
+          <t>6652016</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5449</t>
+          <t>4829</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5677</t>
+          <t>5083</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6885</t>
+          <t>5994</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>448697</t>
+          <t>449317</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>424553</t>
+          <t>425147</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>877491</t>
+          <t>878382</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6005</t>
+          <t>5651</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5171</t>
+          <t>5913</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6150</t>
+          <t>6073</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>681082</t>
+          <t>681436</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>605084</t>
+          <t>604342</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1291192</t>
+          <t>1291269</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7448</t>
+          <t>5968</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7038</t>
+          <t>6275</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -5232,7 +5232,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>440352</t>
+          <t>441832</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>870191</t>
+          <t>870954</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4706</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4650</t>
+          <t>3780</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -5575,7 +5575,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>349290</t>
+          <t>349294</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>659132</t>
+          <t>660002</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7041</t>
+          <t>5923</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>4718</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>381938</t>
+          <t>383056</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>632952</t>
+          <t>634112</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7488</t>
+          <t>6756</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11884</t>
+          <t>11838</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>3192</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14019</t>
+          <t>15800</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,23%</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3419291</t>
+          <t>3420023</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3546425</t>
+          <t>3546471</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3556358</t>
+          <t>3556359</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6971069</t>
+          <t>6969288</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6982088</t>
+          <t>6981896</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,96%</t>
+          <t>99,95%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>2112</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13194</t>
+          <t>12761</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8877</t>
+          <t>11100</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3177</t>
+          <t>3235</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16224</t>
+          <t>16976</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>406269</t>
+          <t>406702</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>417358</t>
+          <t>417351</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>386878</t>
+          <t>384655</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>798994</t>
+          <t>798242</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>812041</t>
+          <t>811983</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -7039,7 +7039,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5120</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6842</t>
+          <t>5974</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>887</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8601</t>
+          <t>7764</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>585376</t>
+          <t>585348</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>556702</t>
+          <t>557570</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1145439</t>
+          <t>1146276</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1153156</t>
+          <t>1153153</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12578</t>
+          <t>11628</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12648</t>
+          <t>11038</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3442</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17469</t>
+          <t>18100</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>656519</t>
+          <t>657469</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>668039</t>
+          <t>668037</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>648738</t>
+          <t>650348</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>660383</t>
+          <t>660386</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1313014</t>
+          <t>1312383</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1327041</t>
+          <t>1327002</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4831</t>
+          <t>4230</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7203</t>
+          <t>6255</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -8211,7 +8211,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>492018</t>
+          <t>492619</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>967564</t>
+          <t>968512</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -8446,7 +8446,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6752</t>
+          <t>7533</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5681</t>
+          <t>6625</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8496,7 +8496,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>371010</t>
+          <t>370229</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -8589,7 +8589,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>706411</t>
+          <t>705467</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5683</t>
+          <t>5684</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5341</t>
+          <t>5647</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8839,7 +8839,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -8862,7 +8862,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>251315</t>
+          <t>251314</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -8932,7 +8932,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>651826</t>
+          <t>651520</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6929</t>
+          <t>6729</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23930</t>
+          <t>23249</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5934</t>
+          <t>5963</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20233</t>
+          <t>20430</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>15227</t>
+          <t>15150</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>36172</t>
+          <t>36591</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3370420</t>
+          <t>3371101</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3387421</t>
+          <t>3387621</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,7 +9220,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3524309</t>
+          <t>3524112</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3538608</t>
+          <t>3538579</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6902720</t>
+          <t>6902301</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6923665</t>
+          <t>6923742</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,7 +9290,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -9665,7 +9665,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>2925</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -9675,12 +9675,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16554</t>
+          <t>12236</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4725</t>
+          <t>6677</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15398</t>
+          <t>18035</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>7933</t>
+          <t>9602</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>2522</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22897</t>
+          <t>23989</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -9778,27 +9778,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>396779</t>
+          <t>404868</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>383433</t>
+          <t>395557</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>308475</t>
+          <t>355835</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>297802</t>
+          <t>344477</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>312875</t>
+          <t>360682</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>705254</t>
+          <t>760703</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>690290</t>
+          <t>746316</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>711224</t>
+          <t>767783</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1558</t>
+          <t>1771</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -10018,7 +10018,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7269</t>
+          <t>9973</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4630</t>
+          <t>4838</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11729</t>
+          <t>12920</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>6188</t>
+          <t>6609</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2208</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15574</t>
+          <t>16159</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -10121,17 +10121,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>421989</t>
+          <t>475119</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>416278</t>
+          <t>466917</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>507463</t>
+          <t>496895</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>500364</t>
+          <t>488813</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>511285</t>
+          <t>500651</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>929452</t>
+          <t>972014</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>920066</t>
+          <t>962464</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>933654</t>
+          <t>976415</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,77%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>8548</t>
+          <t>8881</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3445</t>
+          <t>4154</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17056</t>
+          <t>20261</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6433</t>
+          <t>7716</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3248</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12101</t>
+          <t>13904</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,17 +10421,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>14981</t>
+          <t>16597</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8277</t>
+          <t>9370</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23907</t>
+          <t>26373</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>527790</t>
+          <t>611956</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>519282</t>
+          <t>600576</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>532893</t>
+          <t>616683</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>585569</t>
+          <t>615477</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>579901</t>
+          <t>609289</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>588754</t>
+          <t>619313</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,17 +10534,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1113359</t>
+          <t>1227432</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1104433</t>
+          <t>1217656</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1120063</t>
+          <t>1234659</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10559,7 +10559,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5711</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>2325</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13742</t>
+          <t>13758</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7265</t>
+          <t>7179</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3947</t>
+          <t>3720</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12780</t>
+          <t>12073</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>12976</t>
+          <t>13076</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6854</t>
+          <t>7461</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21783</t>
+          <t>21205</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>882075</t>
+          <t>694720</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>874044</t>
+          <t>686859</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>886282</t>
+          <t>698292</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>705616</t>
+          <t>729707</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>700101</t>
+          <t>724813</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>708934</t>
+          <t>733166</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1587691</t>
+          <t>1424428</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1578884</t>
+          <t>1416299</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1593813</t>
+          <t>1430043</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>5881</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1901</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11386</t>
+          <t>12164</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,22 +11072,22 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6829</t>
+          <t>7538</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3562</t>
+          <t>3960</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12179</t>
+          <t>12917</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -11097,7 +11097,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>11836</t>
+          <t>13418</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7130</t>
+          <t>8147</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19501</t>
+          <t>21126</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>556226</t>
+          <t>603465</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>549848</t>
+          <t>597182</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>559333</t>
+          <t>607332</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,27 +11185,27 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>541076</t>
+          <t>601317</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>535726</t>
+          <t>595938</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>544343</t>
+          <t>604895</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1097303</t>
+          <t>1204784</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1089638</t>
+          <t>1197076</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1102009</t>
+          <t>1210055</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,67 +11380,67 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5413</t>
+          <t>6588</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2444</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>12862</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>3,16%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>2911</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>7050</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
           <t>0,66%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>3,27%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>2742</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>584</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>7013</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>8155</t>
+          <t>9498</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3393</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15084</t>
+          <t>16810</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -11493,67 +11493,67 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>362752</t>
+          <t>400492</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>356117</t>
+          <t>394218</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>365721</t>
+          <t>404224</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>99,3%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>822</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>436255</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>432116</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>438151</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
           <t>99,34%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>822</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>605626</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>601355</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>607784</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>99,55%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>968378</t>
+          <t>836748</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>961449</t>
+          <t>829436</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>973140</t>
+          <t>841003</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,7 +11723,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>930</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4330</t>
+          <t>4688</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,22 +11758,22 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>2304</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>592</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5042</t>
+          <t>5737</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>3059</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1124</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6946</t>
+          <t>7138</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -11836,17 +11836,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>281907</t>
+          <t>309268</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>278429</t>
+          <t>305510</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -11871,27 +11871,27 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>423624</t>
+          <t>462305</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>420789</t>
+          <t>458872</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>425266</t>
+          <t>464017</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>705531</t>
+          <t>771574</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>701644</t>
+          <t>767669</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>707466</t>
+          <t>773679</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,85%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>30299</t>
+          <t>32872</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19346</t>
+          <t>22044</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>44262</t>
+          <t>47690</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>34830</t>
+          <t>39162</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>24327</t>
+          <t>29078</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>47813</t>
+          <t>55356</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>65128</t>
+          <t>72034</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>49201</t>
+          <t>56208</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>84626</t>
+          <t>91698</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3429518</t>
+          <t>3499890</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3415555</t>
+          <t>3485072</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3440471</t>
+          <t>3510718</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3677450</t>
+          <t>3697792</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3664467</t>
+          <t>3681598</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3687953</t>
+          <t>3707876</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>7106969</t>
+          <t>7197682</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7087471</t>
+          <t>7178018</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7122896</t>
+          <t>7213508</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
